--- a/Parth_Salary_Calculation_Gross.xlsx
+++ b/Parth_Salary_Calculation_Gross.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Antigravity\Wilmer House\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BB6889-7719-4600-BE4E-9F9E523F4D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C1F434-34D8-474D-9F1F-5766B6F4E4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Month</t>
   </si>
@@ -63,6 +63,9 @@
     <t>Paid</t>
   </si>
   <si>
+    <t>Ignored</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -78,31 +81,16 @@
     <t>Jul-26</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>--- OVERPAYMENT CALCULATIONS (ON GROSS SALARY) ---</t>
   </si>
   <si>
-    <t>1. Excess GROSS Processed (May &amp; June)</t>
+    <t>1. Excess GROSS Processed (May, June &amp; July)</t>
   </si>
   <si>
     <t>2. Less: Amount Already Recovered from him</t>
   </si>
   <si>
-    <t>3. Remaining GROSS Excess (To be adjusted)</t>
-  </si>
-  <si>
-    <t>--- JULY SETTLEMENT ---</t>
-  </si>
-  <si>
-    <t>4. July Target GROSS Salary</t>
-  </si>
-  <si>
-    <t>5. Less: Remaining GROSS Excess (From point 3)</t>
-  </si>
-  <si>
-    <t>6. FINAL ADJUSTED GROSS (Negative = Still owes)</t>
+    <t>3. FINAL REMAINING GROSS EXCESS TO RECOVER</t>
   </si>
 </sst>
 </file>
@@ -112,7 +100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\£#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,17 +129,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -202,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,8 +194,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -578,14 +554,16 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="H2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3">
         <v>1118.48</v>
@@ -602,14 +580,16 @@
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="H3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3">
         <v>2918.1</v>
@@ -636,7 +616,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3">
         <v>4666.67</v>
@@ -663,7 +643,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3">
         <v>4666.67</v>
@@ -678,7 +658,7 @@
         <v>3682.24</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6" s="3">
         <v>1300</v>
@@ -698,8 +678,8 @@
         <v>17</v>
       </c>
       <c r="E11" s="7">
-        <f>H4+H5</f>
-        <v>4984.7700000000004</v>
+        <f>H4+H5+H6</f>
+        <v>8351.44</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -707,47 +687,16 @@
         <v>18</v>
       </c>
       <c r="E12" s="7">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="10">
         <f>E11-E12</f>
-        <v>3484.7700000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="7">
-        <f>E13</f>
-        <v>3484.7700000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="11">
-        <f>E16-E17</f>
-        <v>-2184.7700000000004</v>
+        <v>6651.4400000000005</v>
       </c>
     </row>
   </sheetData>
